--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-05.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-05.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:Y22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,31 @@
           <t>PnL_R$</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Fonte_Placar</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_stake_u</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Convencao_PnL</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Placar_Original</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Resultado_Original</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -590,17 +615,15 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>?</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
         <v>0.95</v>
       </c>
@@ -609,11 +632,20 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S2" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T2" t="n">
-        <v>19</v>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2x1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -676,17 +708,15 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>5x0</t>
+          <t>?</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
         <v>0.95</v>
       </c>
@@ -695,11 +725,20 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S3" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T3" t="n">
-        <v>19.39</v>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>5x0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -782,10 +821,33 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.95</v>
+        <v>0.19</v>
       </c>
       <c r="T4" t="n">
         <v>19</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>betfair:exato</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2x1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -848,17 +910,15 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>?</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
         <v>0.95</v>
       </c>
@@ -867,11 +927,20 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S5" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T5" t="n">
-        <v>16.97</v>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3x0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -934,17 +1003,15 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>6x0</t>
+          <t>?</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
         <v>0.95</v>
       </c>
@@ -953,11 +1020,20 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S6" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T6" t="n">
-        <v>17.59</v>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>6x0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1020,17 +1096,15 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>?</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="n">
         <v>0.95</v>
       </c>
@@ -1039,11 +1113,20 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S7" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T7" t="n">
-        <v>11.59</v>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1x0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1126,10 +1209,33 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>0.95</v>
+        <v>0.14394</v>
       </c>
       <c r="T8" t="n">
         <v>14.39</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>betfair:exato</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2x0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1212,10 +1318,33 @@
         </is>
       </c>
       <c r="S9" t="n">
+        <v>0.13194</v>
+      </c>
+      <c r="T9" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>betfair:exato</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
         <v>0.95</v>
       </c>
-      <c r="T9" t="n">
-        <v>13.2</v>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>9x1</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1298,10 +1427,33 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>0.95</v>
+        <v>0.17593</v>
       </c>
       <c r="T10" t="n">
         <v>17.59</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>betfair:exato</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4x0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1364,17 +1516,15 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>?</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
         <v>0.95</v>
       </c>
@@ -1383,11 +1533,20 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S11" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T11" t="n">
-        <v>14.39</v>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1450,17 +1609,15 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0x3</t>
+          <t>?</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
         <v>0.95</v>
       </c>
@@ -1469,11 +1626,20 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S12" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T12" t="n">
-        <v>15.32</v>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>0x3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1536,17 +1702,15 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0x3</t>
+          <t>?</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="n">
         <v>0.95</v>
       </c>
@@ -1555,11 +1719,20 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S13" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T13" t="n">
-        <v>13.58</v>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0x3</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1622,17 +1795,15 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>?</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="n">
         <v>0.95</v>
       </c>
@@ -1641,11 +1812,20 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S14" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T14" t="n">
-        <v>5.14</v>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2x1</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1728,10 +1908,33 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>0.95</v>
+        <v>0.16379</v>
       </c>
       <c r="T15" t="n">
         <v>16.38</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>betfair:exato</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2x3</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1794,17 +1997,15 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>?</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>RED</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="n">
         <v>-4.7</v>
       </c>
@@ -1813,11 +2014,20 @@
           <t>RED</t>
         </is>
       </c>
-      <c r="S16" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="T16" t="n">
-        <v>-100</v>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2x1</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1880,17 +2090,15 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>?</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="n">
         <v>0.95</v>
       </c>
@@ -1899,11 +2107,20 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S17" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T17" t="n">
-        <v>14.39</v>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>1x2</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1966,17 +2183,15 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>?</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="n">
         <v>0.95</v>
       </c>
@@ -1985,11 +2200,20 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S18" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T18" t="n">
-        <v>10.79</v>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2x0</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -2052,17 +2276,15 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>?</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="n">
         <v>0.95</v>
       </c>
@@ -2071,11 +2293,20 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S19" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T19" t="n">
-        <v>16.38</v>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>2x0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -2138,17 +2369,15 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>?</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>RED</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="n">
         <v>-6.4</v>
       </c>
@@ -2157,11 +2386,20 @@
           <t>RED</t>
         </is>
       </c>
-      <c r="S20" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="T20" t="n">
-        <v>-100</v>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -2224,17 +2462,15 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>3x3</t>
+          <t>?</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>RED</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="n">
         <v>-4.3</v>
       </c>
@@ -2243,11 +2479,20 @@
           <t>RED</t>
         </is>
       </c>
-      <c r="S21" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>-100</v>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>3x3</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -2310,17 +2555,15 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>?</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>RED</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="n">
         <v>-5</v>
       </c>
@@ -2329,11 +2572,20 @@
           <t>RED</t>
         </is>
       </c>
-      <c r="S22" t="n">
-        <v>-5</v>
-      </c>
-      <c r="T22" t="n">
-        <v>-100</v>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-05.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-05.xlsx
@@ -615,15 +615,17 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
       <c r="Q2" t="n">
         <v>0.95</v>
       </c>
@@ -632,11 +634,25 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T2" t="n">
+        <v>19</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
       <c r="X2" t="inlineStr">
         <is>
           <t>2x1</t>
@@ -708,15 +724,17 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>5x0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
       <c r="Q3" t="n">
         <v>0.95</v>
       </c>
@@ -725,11 +743,25 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>0.19388</v>
+      </c>
+      <c r="T3" t="n">
+        <v>19.39</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
       <c r="X3" t="inlineStr">
         <is>
           <t>5x0</t>
@@ -910,15 +942,17 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
       <c r="Q5" t="n">
         <v>0.95</v>
       </c>
@@ -927,11 +961,25 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>0.16964</v>
+      </c>
+      <c r="T5" t="n">
+        <v>16.96</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr">
         <is>
           <t>3x0</t>
@@ -1003,15 +1051,17 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>6x0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
       <c r="Q6" t="n">
         <v>0.95</v>
       </c>
@@ -1020,11 +1070,25 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>0.17593</v>
+      </c>
+      <c r="T6" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
       <c r="X6" t="inlineStr">
         <is>
           <t>6x0</t>
@@ -1096,15 +1160,17 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
       <c r="Q7" t="n">
         <v>0.95</v>
       </c>
@@ -1113,11 +1179,25 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>0.11585</v>
+      </c>
+      <c r="T7" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
       <c r="X7" t="inlineStr">
         <is>
           <t>1x0</t>
@@ -1516,15 +1596,17 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
       <c r="Q11" t="n">
         <v>0.95</v>
       </c>
@@ -1533,11 +1615,25 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>0.14394</v>
+      </c>
+      <c r="T11" t="n">
+        <v>14.39</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
       <c r="X11" t="inlineStr">
         <is>
           <t>1x1</t>
@@ -1609,15 +1705,17 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>0x3</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
       <c r="Q12" t="n">
         <v>0.95</v>
       </c>
@@ -1626,11 +1724,25 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>0.15323</v>
+      </c>
+      <c r="T12" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
       <c r="X12" t="inlineStr">
         <is>
           <t>0x3</t>
@@ -1702,15 +1814,17 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>0x3</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
       <c r="Q13" t="n">
         <v>0.95</v>
       </c>
@@ -1719,11 +1833,25 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>0.13571</v>
+      </c>
+      <c r="T13" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
       <c r="X13" t="inlineStr">
         <is>
           <t>0x3</t>
@@ -1795,15 +1923,17 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
       <c r="Q14" t="n">
         <v>0.95</v>
       </c>
@@ -1812,11 +1942,25 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>0.05135</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
       <c r="X14" t="inlineStr">
         <is>
           <t>2x1</t>
@@ -1997,15 +2141,17 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
       <c r="Q16" t="n">
         <v>-4.7</v>
       </c>
@@ -2014,11 +2160,25 @@
           <t>RED</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
       <c r="X16" t="inlineStr">
         <is>
           <t>2x1</t>
@@ -2090,15 +2250,17 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
       <c r="Q17" t="n">
         <v>0.95</v>
       </c>
@@ -2107,11 +2269,25 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>0.14394</v>
+      </c>
+      <c r="T17" t="n">
+        <v>14.39</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
       <c r="X17" t="inlineStr">
         <is>
           <t>1x2</t>
@@ -2183,15 +2359,17 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
       <c r="Q18" t="n">
         <v>0.95</v>
       </c>
@@ -2200,11 +2378,25 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>0.10795</v>
+      </c>
+      <c r="T18" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
       <c r="X18" t="inlineStr">
         <is>
           <t>2x0</t>
@@ -2276,15 +2468,17 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
       <c r="Q19" t="n">
         <v>0.95</v>
       </c>
@@ -2293,11 +2487,25 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>0.16379</v>
+      </c>
+      <c r="T19" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
       <c r="X19" t="inlineStr">
         <is>
           <t>2x0</t>
@@ -2369,15 +2577,17 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr"/>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
       <c r="Q20" t="n">
         <v>-6.4</v>
       </c>
@@ -2386,11 +2596,25 @@
           <t>RED</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
       <c r="X20" t="inlineStr">
         <is>
           <t>2x2</t>
@@ -2462,15 +2686,17 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>3x3</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
       <c r="Q21" t="n">
         <v>-4.3</v>
       </c>
@@ -2479,11 +2705,25 @@
           <t>RED</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
       <c r="X21" t="inlineStr">
         <is>
           <t>3x3</t>
@@ -2555,15 +2795,17 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
       <c r="Q22" t="n">
         <v>-5</v>
       </c>
@@ -2572,11 +2814,25 @@
           <t>RED</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>-5</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
       <c r="X22" t="inlineStr">
         <is>
           <t>2x2</t>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-05.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-05.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y22"/>
+  <dimension ref="A1:T22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,31 +529,6 @@
           <t>PnL_R$</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Fonte_Placar</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>PnL_stake_u</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Convencao_PnL</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Placar_Original</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Resultado_Original</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -635,33 +610,10 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>0.19</v>
+        <v>0.95</v>
       </c>
       <c r="T2" t="n">
         <v>19</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2x1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -744,33 +696,10 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0.19388</v>
+        <v>0.95</v>
       </c>
       <c r="T3" t="n">
         <v>19.39</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>5x0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -853,33 +782,10 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.19</v>
+        <v>0.95</v>
       </c>
       <c r="T4" t="n">
         <v>19</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>betfair:exato</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2x1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -962,33 +868,10 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0.16964</v>
+        <v>0.95</v>
       </c>
       <c r="T5" t="n">
-        <v>16.96</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>3x0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
+        <v>16.97</v>
       </c>
     </row>
     <row r="6">
@@ -1071,33 +954,10 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>0.17593</v>
+        <v>0.95</v>
       </c>
       <c r="T6" t="n">
         <v>17.59</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>6x0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
       </c>
     </row>
     <row r="7">
@@ -1180,33 +1040,10 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>0.11585</v>
+        <v>0.95</v>
       </c>
       <c r="T7" t="n">
         <v>11.59</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="V7" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1x0</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
       </c>
     </row>
     <row r="8">
@@ -1289,33 +1126,10 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>0.14394</v>
+        <v>0.95</v>
       </c>
       <c r="T8" t="n">
         <v>14.39</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>betfair:exato</t>
-        </is>
-      </c>
-      <c r="V8" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2x0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
       </c>
     </row>
     <row r="9">
@@ -1398,33 +1212,10 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>0.13194</v>
+        <v>0.95</v>
       </c>
       <c r="T9" t="n">
-        <v>13.19</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>betfair:exato</t>
-        </is>
-      </c>
-      <c r="V9" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>9x1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
+        <v>13.2</v>
       </c>
     </row>
     <row r="10">
@@ -1507,33 +1298,10 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>0.17593</v>
+        <v>0.95</v>
       </c>
       <c r="T10" t="n">
         <v>17.59</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>betfair:exato</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4x0</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
       </c>
     </row>
     <row r="11">
@@ -1616,33 +1384,10 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>0.14394</v>
+        <v>0.95</v>
       </c>
       <c r="T11" t="n">
         <v>14.39</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="V11" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>1x1</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
       </c>
     </row>
     <row r="12">
@@ -1725,33 +1470,10 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>0.15323</v>
+        <v>0.95</v>
       </c>
       <c r="T12" t="n">
         <v>15.32</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>0x3</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
       </c>
     </row>
     <row r="13">
@@ -1834,33 +1556,10 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>0.13571</v>
+        <v>0.95</v>
       </c>
       <c r="T13" t="n">
-        <v>13.57</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>0x3</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
+        <v>13.58</v>
       </c>
     </row>
     <row r="14">
@@ -1943,33 +1642,10 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>0.05135</v>
+        <v>0.95</v>
       </c>
       <c r="T14" t="n">
         <v>5.14</v>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="V14" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>2x1</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
       </c>
     </row>
     <row r="15">
@@ -2052,33 +1728,10 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>0.16379</v>
+        <v>0.95</v>
       </c>
       <c r="T15" t="n">
         <v>16.38</v>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>betfair:exato</t>
-        </is>
-      </c>
-      <c r="V15" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>2x3</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
       </c>
     </row>
     <row r="16">
@@ -2161,33 +1814,10 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>-1</v>
+        <v>-4.7</v>
       </c>
       <c r="T16" t="n">
         <v>-100</v>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="V16" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>2x1</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>RED</t>
-        </is>
       </c>
     </row>
     <row r="17">
@@ -2270,33 +1900,10 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>0.14394</v>
+        <v>0.95</v>
       </c>
       <c r="T17" t="n">
         <v>14.39</v>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="V17" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>1x2</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
       </c>
     </row>
     <row r="18">
@@ -2379,33 +1986,10 @@
         </is>
       </c>
       <c r="S18" t="n">
-        <v>0.10795</v>
+        <v>0.95</v>
       </c>
       <c r="T18" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="V18" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>2x0</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
+        <v>10.79</v>
       </c>
     </row>
     <row r="19">
@@ -2488,33 +2072,10 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>0.16379</v>
+        <v>0.95</v>
       </c>
       <c r="T19" t="n">
         <v>16.38</v>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="V19" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>2x0</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
       </c>
     </row>
     <row r="20">
@@ -2597,33 +2158,10 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>-1</v>
+        <v>-6.4</v>
       </c>
       <c r="T20" t="n">
         <v>-100</v>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="V20" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>2x2</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>RED</t>
-        </is>
       </c>
     </row>
     <row r="21">
@@ -2706,33 +2244,10 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>-1</v>
+        <v>-4.3</v>
       </c>
       <c r="T21" t="n">
         <v>-100</v>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="V21" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>3x3</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>RED</t>
-        </is>
       </c>
     </row>
     <row r="22">
@@ -2815,33 +2330,10 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="T22" t="n">
         <v>-100</v>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="V22" t="n">
-        <v>-5</v>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>2x2</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>RED</t>
-        </is>
       </c>
     </row>
   </sheetData>
